--- a/AAPL_Model.xlsx
+++ b/AAPL_Model.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Input" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="307">
   <si>
     <t xml:space="preserve">DATA INPUT - historical financials. Fixed row keys in column A; one column per year. A Python extractor should write ONLY this tab. (You may hide this tab.)</t>
   </si>
@@ -642,286 +642,202 @@
     <t xml:space="preserve">  * FY2025 interest expense: source reported ZERO against 112.4bn of debt (issuer nets interest inside 'other income/(expense)'). ESTIMATED at 3.17% = the company's own last observed effective rate, giving 3.6bn. Not a reported figure - replace with the 10-K note when available.</t>
   </si>
   <si>
-    <t xml:space="preserve">Institutional Valuation Layer - EPS-Power x Multiple (street-comparable lens)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The FCF DCF above is the fundamental anchor. This layer prices FORWARD EPS POWER at scenario multiples - how the street values megacaps. The gap between the two lenses IS the multiple bet: printed, never blended.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS - cash-return convention (today's diluted count)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS - street count-shrink view (buybacks retire stock at today's price)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diluted count, street view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS x Multiple - Scenario Valuation (forward value, discounted at the hurdle)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurdle (CAPM, 12-mo convention)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor year: 3 (K)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor EPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forward Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PV Today</t>
+    <t xml:space="preserve">Catalyst Odds (judgmental - the odds ARE the thesis; news scan as-of in attestation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foldable iPhone supercycle lands FY26-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upside to the deck's own unit and ASP path, not the base case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Services growth holds &gt;=12%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mix shift carries gross margin; core margin thesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Siri monetization visible by FY27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unpriced optionality - no revenue for it in the forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOJ antitrust settles without Services-model damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early talks reported 17-Jul; removes the App Store tail-risk discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buybacks sustain &gt;=$100B/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funds the per-share compounding; modeled as an equity outflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenAI lawsuit escalates into platform conflict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade-secrets suit filed Jul-2026; overlay risk, not in the deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Capital Build - the discount rate is DERIVED here, not asserted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government bond yield (United States 10Y, as-of 2026-07-17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less: sovereign default spread (Aa1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISK-FREE RATE in USD (bond yield less sovereign spread)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity risk premium (Damodaran country ERP table, last updated Jan-2026 (stern.nyu.edu/~adamodar), fetched 2026-07-19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implied MARKET RETURN  Rm = rf + ERP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country risk premium (already inside the ERP above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levered beta (adjusted)  [raw 1.097]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size / illiquidity premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of equity = rf + beta x (ERP + CRP) + size premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year-1 WACC used in the DCF grid (row 149) - cross-check they agree; the grid fades toward the mature rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of debt - pre-tax (marginal, = rf + credit spread)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marginal: rf-equivalent + credit spread; after-tax at the MARGINAL rate 25% (not the effective rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of debt - after tax  = pre-tax x (1 - tax rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC = CoE x (1-Wd) + Kd(after-tax) x Wd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal growth vs risk-free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damodaran convention for MATURE-MARKET compounders: terminal g = the risk-free rate (an economy cannot outgrow its own bond) - a gap there means one input is stale. For declining or finite-resource industries (coal, EM cyclicals) terminal g SHOULD sit well below rf; the gap is then deliberate, not an error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional premium: none - the model discounts at the derived build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC USED IN THE MODEL (build + named premium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tie-out vs the DCF grid (year-1 WACC, row 149)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must be 0.00%. A non-zero tie-out means the discount rate is asserted, not derived - any premium above the CAPM build must be NAMED above, never silent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital structure at MARKET values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight of debt   Wd = D / (D + E)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market values: gross debt 112.4 / (debt + mcap 4,902.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight of equity We = 1 - Wd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check: We + Wd must equal 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity contribution  = CoE x We</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt contribution    = Kd(after-tax) x Wd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum = WACC (must equal the build above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt weight uses GROSS debt at book vs equity at MARKET (standard); a net-debt weight would be negative for net-cash names and is not used. Cost of debt is the MARGINAL rate today, not the legacy coupon - old ZIRP-era bonds understate what new borrowing costs and must never set the WACC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charts and Graphs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Margin (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sensitivity &amp; Scenarios - NASDAQ: AAPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All figures in USD billions | per-share values in USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid 1: Intrinsic Value per Share - WACC (rows) x Perpetual Growth (columns) - perpetuity TV only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid 2: Intrinsic Value per Share - WACC (rows) x Exit EV/EBITDA (columns) - exit-multiple TV only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid 3: Intrinsic Value per Share - WACC (rows) x FCF Deck Scale (columns) - stresses the revenue/margin deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scales every forecast cash flow and the terminal value by the column factor - the growth deck is usually where the real risk lives, not the discount rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenarios: Implied Value per Share - Bear / Base / Bull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear = higher WACC, lower terminal growth; Bull = the reverse. Blue offsets are editable. Terminal value = average of perpetuity and exit-multiple, like the DCF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth</t>
   </si>
   <si>
     <t xml:space="preserve">Prob.</t>
   </si>
   <si>
-    <t xml:space="preserve">Contribution</t>
+    <t xml:space="preserve">Bear implied EV</t>
   </si>
   <si>
     <t xml:space="preserve">Bear</t>
   </si>
   <si>
+    <t xml:space="preserve">Base implied EV</t>
+  </si>
+  <si>
     <t xml:space="preserve">Base</t>
   </si>
   <si>
+    <t xml:space="preserve">Bull implied EV</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme Bull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PWFV (EPS-anchored, PV today)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vs DCF PWFV (Sensitivity!B46) and vs price D135 - the spread between the two PWFVs is the multiple bet, held vs faded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor = FY2028 EPS. Bear = deck conversion (no supercycle premium); base = deck/street midpoint; bull = street avg ($10.70, 18-20 analysts); x-bull = street high. Multiples from AAPL's own 10-yr forward-P/E range (~18-36x): bear 22x (post-2018 trough zone), base 28x, bull 32x (recent regime), x-bull 36x (today's, held). Hurdle 9% ~ CAPM (rf 4.3% + beta ~1.05 x ERP 4.6%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Street Reconciliation (consensus vs this deck)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Street Revenue (consensus avg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deck vs Street - Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Street EPS (consensus avg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deck vs Street - EPS (count-shrink view)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where we differ: Deck sits ~8% below street on FY26-27 revenue - street prices a foldable/AI supercycle, deck anchors to guidance momentum with a gentle fade - and ~6% below on near-year EPS conversion. Beyond FY28 the deck fades while street holds. The REST of the price gap is the multiple: street pays ~30x+ forward EPS; the deck's terminal implies 18-20x EV/EBITDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consensus price target: 328.83 (median 330, range 250-400) as-of 2026-07-17 - a 12-mo FORWARD value; compare to our PV x (1+hurdle).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: FMP consensus estimates (28-32 analysts FY26-27; 18-20 FY28) (2026-07-17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalyst Odds (judgmental - the odds ARE the thesis; news scan as-of in attestation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foldable iPhone supercycle lands FY26-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Street's revenue premise; deck treats it as upside, not base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Services growth holds &gt;=12%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mix shift carries gross margin; core margin thesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Siri monetization visible by FY27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The priced optionality sponsoring the multiple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOJ antitrust settles without Services-model damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Early talks reported 17-Jul; removes the App Store tail-risk discount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buybacks sustain &gt;=$100B/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funds the count-shrink EPS convention street uses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple holds &gt;=30x forward through FY28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE swing node - this single belief is the entire DCF-vs-street gap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpenAI lawsuit escalates into platform conflict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trade-secrets suit filed Jul-2026; overlay risk, not in the deck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of Capital Build - the discount rate is DERIVED here, not asserted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Government bond yield (United States 10Y, as-of 2026-07-17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Less: sovereign default spread (Aa1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RISK-FREE RATE in USD (bond yield less sovereign spread)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity risk premium (Damodaran country ERP table, last updated Jan-2026 (stern.nyu.edu/~adamodar), fetched 2026-07-19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implied MARKET RETURN  Rm = rf + ERP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country risk premium (already inside the ERP above)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levered beta (adjusted)  [raw 1.097]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size / illiquidity premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of equity = rf + beta x (ERP + CRP) + size premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year-1 WACC used in the DCF grid (row 149) - cross-check they agree; the grid fades toward the mature rate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of debt - pre-tax (marginal, = rf + credit spread)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marginal: rf-equivalent + credit spread; after-tax at the MARGINAL rate 25% (not the effective rate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of debt - after tax  = pre-tax x (1 - tax rate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACC = CoE x (1-Wd) + Kd(after-tax) x Wd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal growth vs risk-free</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damodaran convention for MATURE-MARKET compounders: terminal g = the risk-free rate (an economy cannot outgrow its own bond) - a gap there means one input is stale. For declining or finite-resource industries (coal, EM cyclicals) terminal g SHOULD sit well below rf; the gap is then deliberate, not an error.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional premium: none - the model discounts at the derived build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACC USED IN THE MODEL (build + named premium)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tie-out vs the DCF grid (year-1 WACC, row 149)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 0.00%. A non-zero tie-out means the discount rate is asserted, not derived - any premium above the CAPM build must be NAMED above, never silent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital structure at MARKET values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight of debt   Wd = D / (D + E)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market values: gross debt 112.4 / (debt + mcap 4,902.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight of equity We = 1 - Wd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check: We + Wd must equal 100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity contribution  = CoE x We</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt contribution    = Kd(after-tax) x Wd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum = WACC (must equal the build above)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt weight uses GROSS debt at book vs equity at MARKET (standard); a net-debt weight would be negative for net-cash names and is not used. Cost of debt is the MARGINAL rate today, not the legacy coupon - old ZIRP-era bonds understate what new borrowing costs and must never set the WACC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charts and Graphs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross Profit Margin (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sensitivity &amp; Scenarios - NASDAQ: AAPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All figures in USD billions | per-share values in USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid 1: Intrinsic Value per Share - WACC (rows) x Perpetual Growth (columns) - perpetuity TV only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid 2: Intrinsic Value per Share - WACC (rows) x Exit EV/EBITDA (columns) - exit-multiple TV only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid 3: Intrinsic Value per Share - WACC (rows) x FCF Deck Scale (columns) - stresses the revenue/margin deck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scales every forecast cash flow and the terminal value by the column factor - the growth deck is usually where the real risk lives, not the discount rate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenarios: Implied Value per Share - Bear / Base / Bull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear = higher WACC, lower terminal growth; Bull = the reverse. Blue offsets are editable. Terminal value = average of perpetuity and exit-multiple, like the DCF.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Today</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear implied EV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base implied EV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bull implied EV</t>
   </si>
   <si>
     <t xml:space="preserve">Current Price</t>
@@ -1054,6 +970,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1073,78 +990,86 @@
     <font>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000CC"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <color theme="1"/>
+      <color rgb="FF2E5B9F"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1162,9 +1087,10 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1428,15 +1354,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1484,7 +1402,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1576,6 +1502,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="10"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1787,8 +1714,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="38604395"/>
-        <c:axId val="76323062"/>
+        <c:axId val="26688858"/>
+        <c:axId val="52353530"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1963,7 +1890,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:hiLowLines>
           <c:spPr>
@@ -1973,11 +1900,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="75632239"/>
-        <c:axId val="37051955"/>
+        <c:axId val="63878330"/>
+        <c:axId val="87922663"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="38604395"/>
+        <c:axId val="26688858"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2010,7 +1937,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76323062"/>
+        <c:crossAx val="52353530"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2018,7 +1945,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76323062"/>
+        <c:axId val="52353530"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2061,12 +1988,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38604395"/>
+        <c:crossAx val="26688858"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="75632239"/>
+        <c:axId val="63878330"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2099,7 +2026,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37051955"/>
+        <c:crossAx val="87922663"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2107,7 +2034,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37051955"/>
+        <c:axId val="87922663"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2140,7 +2067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75632239"/>
+        <c:crossAx val="63878330"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2730,11 +2657,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="-20"/>
-        <c:axId val="24218837"/>
-        <c:axId val="22257888"/>
+        <c:axId val="99515413"/>
+        <c:axId val="74412311"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24218837"/>
+        <c:axId val="99515413"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2767,7 +2694,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22257888"/>
+        <c:crossAx val="74412311"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2775,7 +2702,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22257888"/>
+        <c:axId val="74412311"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2818,7 +2745,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24218837"/>
+        <c:crossAx val="99515413"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3045,7 +2972,7 @@
                   <c:v>202.487993734965</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>212.840297920143</c:v>
+                  <c:v>212.840297920142</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>223.645397417908</c:v>
@@ -3184,7 +3111,7 @@
                   <c:v>228.030220556419</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>238.312728504045</c:v>
+                  <c:v>238.312728504044</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>248.94301908588</c:v>
@@ -3199,7 +3126,7 @@
                   <c:v>282.834408413825</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>294.853097219643</c:v>
+                  <c:v>294.853097219642</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>307.228341550065</c:v>
@@ -3326,7 +3253,7 @@
                   <c:v>375.088922900303</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>378.117879120535</c:v>
+                  <c:v>378.117879120534</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>394.361313610015</c:v>
@@ -3338,7 +3265,7 @@
                   <c:v>428.592991000663</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>446.565639569944</c:v>
+                  <c:v>446.565639569943</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>465.128578551665</c:v>
@@ -3353,7 +3280,7 @@
                   <c:v>524.522568144817</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>545.660356082121</c:v>
+                  <c:v>545.66035608212</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3518,11 +3445,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="73703705"/>
-        <c:axId val="49082461"/>
+        <c:axId val="35048536"/>
+        <c:axId val="22686572"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="73703705"/>
+        <c:axId val="35048536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3555,7 +3482,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49082461"/>
+        <c:crossAx val="22686572"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3563,7 +3490,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49082461"/>
+        <c:axId val="22686572"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3606,7 +3533,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73703705"/>
+        <c:crossAx val="35048536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4321,8 +4248,8 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>810360</xdr:colOff>
-      <xdr:row>304</xdr:row>
-      <xdr:rowOff>123120</xdr:rowOff>
+      <xdr:row>302</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4330,7 +4257,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="48150720"/>
+        <a:off x="0" y="44517960"/>
         <a:ext cx="5039640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -4351,8 +4278,8 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>105840</xdr:colOff>
-      <xdr:row>304</xdr:row>
-      <xdr:rowOff>123120</xdr:rowOff>
+      <xdr:row>302</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4360,7 +4287,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8176320" y="48150720"/>
+        <a:off x="8176320" y="44517960"/>
         <a:ext cx="5039640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -4386,8 +4313,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>198720</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>94320</xdr:rowOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>170640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4395,7 +4322,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="8706960"/>
+        <a:off x="0" y="9392760"/>
         <a:ext cx="6119640" cy="3599640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -4452,14 +4379,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -4467,25 +4394,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -4503,12 +4463,48 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -4521,19 +4517,18 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -4556,12 +4551,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -4584,7 +4579,7 @@
         <v>416.161</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -4607,7 +4602,7 @@
         <v>220.96</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -4630,7 +4625,7 @@
         <v>28.047</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -4653,7 +4648,7 @@
         <v>22.406</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -4676,7 +4671,7 @@
         <v>11.698</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
@@ -4699,7 +4694,7 @@
         <v>3.5664</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
@@ -4722,12 +4717,12 @@
         <v>20.719</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -4750,7 +4745,7 @@
         <v>132.42</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
@@ -4773,7 +4768,7 @@
         <v>72.957</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -4796,7 +4791,7 @@
         <v>5.718</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
@@ -4819,7 +4814,7 @@
         <v>148.146</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -4842,7 +4837,7 @@
         <v>173.131</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
@@ -4865,7 +4860,7 @@
         <v>112.377</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -4888,7 +4883,7 @@
         <v>87.997</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
@@ -4911,12 +4906,12 @@
         <v>-14.264</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>41</v>
       </c>
@@ -4939,7 +4934,7 @@
         <v>12.715</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>43</v>
       </c>
@@ -4962,7 +4957,7 @@
         <v>-8.483</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
@@ -4985,12 +4980,12 @@
         <v>-90.711</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>48</v>
       </c>
@@ -5001,7 +4996,7 @@
         <v>102.599</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>50</v>
       </c>
@@ -5012,7 +5007,7 @@
         <v>123.857</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>52</v>
       </c>
@@ -5040,8 +5035,8 @@
     <tabColor rgb="FF2E5B9F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S286"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S282"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="2"/>
@@ -5126,7 +5121,7 @@
       </c>
       <c r="S2" s="8"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
         <v>72</v>
       </c>
@@ -5191,7 +5186,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
         <v>73</v>
       </c>
@@ -5224,8 +5219,7 @@
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
         <v>77</v>
       </c>
@@ -5248,7 +5242,7 @@
       <c r="R7" s="19"/>
       <c r="S7" s="19"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>78</v>
       </c>
@@ -5299,7 +5293,7 @@
         <v>0.043</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>79</v>
       </c>
@@ -5354,7 +5348,7 @@
         <v>0.516</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>80</v>
       </c>
@@ -5409,7 +5403,7 @@
         <v>0.0634</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>81</v>
       </c>
@@ -5464,7 +5458,7 @@
         <v>34.39</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>82</v>
       </c>
@@ -5519,7 +5513,7 @@
         <v>0.079</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>83</v>
       </c>
@@ -5574,7 +5568,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>84</v>
       </c>
@@ -5629,7 +5623,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>85</v>
       </c>
@@ -5684,7 +5678,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>86</v>
       </c>
@@ -5739,7 +5733,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>87</v>
       </c>
@@ -5794,7 +5788,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>88</v>
       </c>
@@ -5849,7 +5843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>89</v>
       </c>
@@ -5904,7 +5898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>90</v>
       </c>
@@ -5959,7 +5953,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
@@ -6009,8 +6003,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
         <v>92</v>
@@ -6034,8 +6026,7 @@
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
@@ -6100,7 +6091,7 @@
         <v>679.077704260633</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>93</v>
       </c>
@@ -6165,7 +6156,7 @@
         <v>350.404095398486</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>94</v>
       </c>
@@ -6230,12 +6221,12 @@
         <v>328.673608862146</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>96</v>
       </c>
@@ -6300,7 +6291,7 @@
         <v>43.0535264501241</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>97</v>
       </c>
@@ -6365,7 +6356,7 @@
         <v>34.39</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>98</v>
       </c>
@@ -6430,7 +6421,7 @@
         <v>13.205446832109</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
         <v>20</v>
       </c>
@@ -6495,7 +6486,7 @@
         <v>3.37131</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>99</v>
       </c>
@@ -6560,7 +6551,7 @@
         <v>94.0202832822331</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>100</v>
       </c>
@@ -6625,8 +6616,7 @@
         <v>234.653325579913</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>22</v>
       </c>
@@ -6691,7 +6681,7 @@
         <v>39.8910653485852</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>101</v>
       </c>
@@ -6756,8 +6746,6 @@
         <v>194.762260231328</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
         <v>102</v>
@@ -6781,13 +6769,12 @@
       <c r="R41" s="16"/>
       <c r="S41" s="16"/>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>25</v>
       </c>
@@ -6852,7 +6839,7 @@
         <v>661.128017292385</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>27</v>
       </c>
@@ -6917,7 +6904,7 @@
         <v>107.908237937306</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>29</v>
       </c>
@@ -6982,7 +6969,7 @@
         <v>9.60011220269826</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
         <v>104</v>
       </c>
@@ -7047,7 +7034,7 @@
         <v>168.952108004714</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>105</v>
       </c>
@@ -7112,13 +7099,12 @@
         <v>947.588475437103</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
         <v>33</v>
       </c>
@@ -7183,7 +7169,7 @@
         <v>275.52322021744</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>35</v>
       </c>
@@ -7248,7 +7234,7 @@
         <v>112.377</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
         <v>107</v>
       </c>
@@ -7313,12 +7299,12 @@
         <v>387.90022021744</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
         <v>37</v>
       </c>
@@ -7383,7 +7369,7 @@
         <v>-962.003</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>39</v>
       </c>
@@ -7448,7 +7434,7 @@
         <v>1521.69125521966</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>108</v>
       </c>
@@ -7513,7 +7499,7 @@
         <v>559.688255219663</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>109</v>
       </c>
@@ -7578,8 +7564,7 @@
         <v>947.588475437103</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
         <v>110</v>
       </c>
@@ -7644,8 +7629,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
         <v>111</v>
@@ -7669,13 +7652,12 @@
       <c r="R63" s="16"/>
       <c r="S63" s="16"/>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>101</v>
       </c>
@@ -7736,7 +7718,7 @@
         <v>194.762260231328</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
         <v>113</v>
       </c>
@@ -7797,7 +7779,7 @@
         <v>13.205446832109</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
         <v>114</v>
       </c>
@@ -7858,7 +7840,7 @@
         <v>-5.52629884213073</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
         <v>115</v>
       </c>
@@ -7919,13 +7901,12 @@
         <v>213.494005905568</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
         <v>117</v>
       </c>
@@ -7986,7 +7967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
         <v>118</v>
       </c>
@@ -8047,13 +8028,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
         <v>120</v>
       </c>
@@ -8114,7 +8094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
         <v>121</v>
       </c>
@@ -8175,7 +8155,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>122</v>
       </c>
@@ -8236,8 +8216,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
         <v>123</v>
       </c>
@@ -8298,7 +8277,7 @@
         <v>93.4940059055676</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
         <v>124</v>
       </c>
@@ -8359,7 +8338,7 @@
         <v>567.634011386818</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
         <v>125</v>
       </c>
@@ -8420,13 +8399,11 @@
         <v>661.128017292385</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="86" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="15" t="s">
         <v>127</v>
@@ -8450,13 +8427,12 @@
       <c r="R86" s="16"/>
       <c r="S86" s="16"/>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
         <v>27</v>
       </c>
@@ -8521,7 +8497,7 @@
         <v>107.908237937306</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
         <v>29</v>
       </c>
@@ -8586,7 +8562,7 @@
         <v>9.60011220269826</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
         <v>33</v>
       </c>
@@ -8651,7 +8627,7 @@
         <v>275.52322021744</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
         <v>129</v>
       </c>
@@ -8716,7 +8692,7 @@
         <v>-158.014870077436</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
         <v>130</v>
       </c>
@@ -8781,13 +8757,12 @@
         <v>-5.52629884213073</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
         <v>132</v>
       </c>
@@ -8852,7 +8827,7 @@
         <v>167.157554836823</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
         <v>133</v>
       </c>
@@ -8917,7 +8892,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
         <v>134</v>
       </c>
@@ -8982,7 +8957,7 @@
         <v>13.205446832109</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
         <v>135</v>
       </c>
@@ -9047,13 +9022,12 @@
         <v>168.952108004714</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
         <v>137</v>
       </c>
@@ -9118,7 +9092,7 @@
         <v>112.377</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
         <v>138</v>
       </c>
@@ -9183,7 +9157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
         <v>139</v>
       </c>
@@ -9248,7 +9222,7 @@
         <v>112.377</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
         <v>140</v>
       </c>
@@ -9313,13 +9287,12 @@
         <v>3.37131</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
         <v>142</v>
       </c>
@@ -9364,7 +9337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
         <v>143</v>
       </c>
@@ -9409,7 +9382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
         <v>144</v>
       </c>
@@ -9454,8 +9427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="18" t="s">
         <v>145</v>
       </c>
@@ -9478,28 +9450,26 @@
       <c r="R112" s="19"/>
       <c r="S112" s="19"/>
     </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="116" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="117" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="118" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="119" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="120" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="121" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="122" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="123" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="124" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="125" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="126" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="127" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="128" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="129" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="130" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="131" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="15" t="s">
         <v>147</v>
@@ -9523,8 +9493,7 @@
       <c r="R131" s="16"/>
       <c r="S131" s="16"/>
     </row>
-    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="18" t="s">
         <v>148</v>
       </c>
@@ -9547,7 +9516,7 @@
       <c r="R133" s="19"/>
       <c r="S133" s="19"/>
     </row>
-    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
         <v>149</v>
       </c>
@@ -9555,7 +9524,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
         <v>150</v>
       </c>
@@ -9563,7 +9532,7 @@
         <v>333.74</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
         <v>151</v>
       </c>
@@ -9571,7 +9540,7 @@
         <v>14.688</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
         <v>152</v>
       </c>
@@ -9580,7 +9549,7 @@
         <v>4901.97312</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
         <v>153</v>
       </c>
@@ -9588,7 +9557,7 @@
         <v>0.0432</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
         <v>154</v>
       </c>
@@ -9596,7 +9565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
         <v>155</v>
       </c>
@@ -9604,7 +9573,7 @@
         <v>4901.97</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
         <v>156</v>
       </c>
@@ -9612,8 +9581,7 @@
         <v>14.688</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="18" t="s">
         <v>157</v>
       </c>
@@ -9636,7 +9604,7 @@
       <c r="R143" s="19"/>
       <c r="S143" s="19"/>
     </row>
-    <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H144" s="2" t="s">
         <v>158</v>
       </c>
@@ -9644,7 +9612,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
         <v>160</v>
       </c>
@@ -9695,7 +9663,7 @@
         <v>49578</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
         <v>161</v>
       </c>
@@ -9730,7 +9698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
         <v>162</v>
       </c>
@@ -9775,7 +9743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
         <v>163</v>
       </c>
@@ -9820,7 +9788,7 @@
         <v>9.1972602739726</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
         <v>164</v>
       </c>
@@ -9855,7 +9823,7 @@
         <v>0.0866</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
         <v>165</v>
       </c>
@@ -9900,7 +9868,7 @@
         <v>0.460677278511099</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
         <v>166</v>
       </c>
@@ -9945,7 +9913,7 @@
         <v>238.024635579913</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
         <v>167</v>
       </c>
@@ -9990,7 +9958,7 @@
         <v>-40.4641880485852</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
         <v>168</v>
       </c>
@@ -10035,7 +10003,7 @@
         <v>13.205446832109</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
         <v>169</v>
       </c>
@@ -10080,7 +10048,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
         <v>170</v>
       </c>
@@ -10125,7 +10093,7 @@
         <v>5.52629884213073</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
         <v>171</v>
       </c>
@@ -10170,7 +10138,7 @@
         <v>201.292193205568</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
         <v>172</v>
       </c>
@@ -10183,7 +10151,7 @@
         <v>4680.28751534931</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
         <v>173</v>
       </c>
@@ -10235,7 +10203,7 @@
         <v>4680.28751534931</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
         <v>173</v>
       </c>
@@ -10288,8 +10256,7 @@
         <v>4680.28751534931</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="18" t="s">
         <v>174</v>
       </c>
@@ -10312,7 +10279,7 @@
       <c r="R161" s="19"/>
       <c r="S161" s="19"/>
     </row>
-    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
         <v>175</v>
       </c>
@@ -10321,7 +10288,7 @@
         <v>4838.43354728222</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
         <v>176</v>
       </c>
@@ -10330,7 +10297,7 @@
         <v>4522.1414834164</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
         <v>177</v>
       </c>
@@ -10339,7 +10306,7 @@
         <v>4680.28751534931</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
         <v>178</v>
       </c>
@@ -10355,7 +10322,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="18" t="s">
         <v>180</v>
       </c>
@@ -10378,7 +10345,7 @@
       <c r="R166" s="19"/>
       <c r="S166" s="19"/>
     </row>
-    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
         <v>181</v>
       </c>
@@ -10387,7 +10354,7 @@
         <v>3125.1011237374</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
         <v>182</v>
       </c>
@@ -10396,7 +10363,7 @@
         <v>132.42</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
         <v>183</v>
       </c>
@@ -10405,7 +10372,7 @@
         <v>112.377</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
         <v>184</v>
       </c>
@@ -10414,7 +10381,7 @@
         <v>3145.1441237374</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
         <v>185</v>
       </c>
@@ -10423,8 +10390,7 @@
         <v>214.130182716326</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="18" t="s">
         <v>186</v>
       </c>
@@ -10447,7 +10413,7 @@
       <c r="R173" s="19"/>
       <c r="S173" s="19"/>
     </row>
-    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
         <v>187</v>
       </c>
@@ -10456,7 +10422,7 @@
         <v>4901.97312</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
         <v>188</v>
       </c>
@@ -10465,7 +10431,7 @@
         <v>112.377</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
         <v>189</v>
       </c>
@@ -10474,7 +10440,7 @@
         <v>132.42</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
         <v>190</v>
       </c>
@@ -10483,7 +10449,7 @@
         <v>4881.93012</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
         <v>150</v>
       </c>
@@ -10492,8 +10458,7 @@
         <v>333.74</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="18" t="s">
         <v>191</v>
       </c>
@@ -10516,7 +10481,7 @@
       <c r="R180" s="19"/>
       <c r="S180" s="19"/>
     </row>
-    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
         <v>192</v>
       </c>
@@ -10525,7 +10490,7 @@
         <v>-0.358392213350734</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
         <v>193</v>
       </c>
@@ -10534,7 +10499,7 @@
         <v>0.029093703189469</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
         <v>194</v>
       </c>
@@ -10546,7 +10511,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="18" t="s">
         <v>196</v>
       </c>
@@ -10569,7 +10534,7 @@
       <c r="R184" s="19"/>
       <c r="S184" s="19"/>
     </row>
-    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
         <v>197</v>
       </c>
@@ -10614,7 +10579,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
         <v>198</v>
       </c>
@@ -10628,7 +10593,7 @@
       </c>
       <c r="K186" s="22" t="n">
         <f aca="false">J186*(1+K149)^K147-K158</f>
-        <v>3459.96863558411</v>
+        <v>3459.9686355841</v>
       </c>
       <c r="L186" s="22" t="n">
         <f aca="false">K186*(1+L149)^L147-L158</f>
@@ -10648,18 +10613,18 @@
       </c>
       <c r="P186" s="22" t="n">
         <f aca="false">O186*(1+P149)^P147-P158</f>
-        <v>4309.5694605263</v>
+        <v>4309.56946052629</v>
       </c>
       <c r="Q186" s="22" t="n">
         <f aca="false">P186*(1+Q149)^Q147-Q158</f>
-        <v>4492.52688068736</v>
+        <v>4492.52688068735</v>
       </c>
       <c r="R186" s="22" t="n">
         <f aca="false">Q186*(1+R149)^R147-R158</f>
         <v>4680.28751534931</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="s">
         <v>199</v>
       </c>
@@ -10673,7 +10638,7 @@
       </c>
       <c r="K187" s="25" t="n">
         <f aca="false">K186+$H$44-$H$52</f>
-        <v>3480.01163558411</v>
+        <v>3480.0116355841</v>
       </c>
       <c r="L187" s="25" t="n">
         <f aca="false">L186+$H$44-$H$52</f>
@@ -10693,7 +10658,7 @@
       </c>
       <c r="P187" s="25" t="n">
         <f aca="false">P186+$H$44-$H$52</f>
-        <v>4329.6124605263</v>
+        <v>4329.61246052629</v>
       </c>
       <c r="Q187" s="25" t="n">
         <f aca="false">Q186+$H$44-$H$52</f>
@@ -10704,7 +10669,7 @@
         <v>4700.33051534931</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
         <v>200</v>
       </c>
@@ -10749,555 +10714,149 @@
         <v>320.011609160492</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="14" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="14" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="14" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="200" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="15" t="s">
+      <c r="A200" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="B200" s="16"/>
-      <c r="C200" s="16"/>
-      <c r="D200" s="16"/>
-      <c r="E200" s="16"/>
-      <c r="F200" s="16"/>
-      <c r="G200" s="16"/>
-      <c r="H200" s="16"/>
-      <c r="I200" s="16"/>
-      <c r="J200" s="16"/>
-      <c r="K200" s="16"/>
-      <c r="L200" s="16"/>
-      <c r="M200" s="16"/>
-      <c r="N200" s="16"/>
-      <c r="O200" s="16"/>
-      <c r="P200" s="16"/>
-      <c r="Q200" s="16"/>
-      <c r="R200" s="16"/>
-      <c r="S200" s="16"/>
-    </row>
-    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="1" t="s">
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="2" t="s">
         <v>207</v>
       </c>
+      <c r="F201" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="I202" s="25" t="n">
-        <f aca="false">I38/$D$136</f>
-        <v>7.8476479048829</v>
-      </c>
-      <c r="J202" s="25" t="n">
-        <f aca="false">J38/$D$136</f>
-        <v>8.33329917914864</v>
-      </c>
-      <c r="K202" s="25" t="n">
-        <f aca="false">K38/$D$136</f>
-        <v>8.9302247806159</v>
-      </c>
-      <c r="L202" s="25" t="n">
-        <f aca="false">L38/$D$136</f>
-        <v>9.5035765815711</v>
-      </c>
-      <c r="M202" s="25" t="n">
-        <f aca="false">M38/$D$136</f>
-        <v>10.117849399208</v>
-      </c>
-      <c r="N202" s="25" t="n">
-        <f aca="false">N38/$D$136</f>
-        <v>10.6985747952586</v>
-      </c>
-      <c r="O202" s="25" t="n">
-        <f aca="false">O38/$D$136</f>
-        <v>11.3302819381905</v>
-      </c>
-      <c r="P202" s="25" t="n">
-        <f aca="false">P38/$D$136</f>
-        <v>11.9407980710773</v>
-      </c>
-      <c r="Q202" s="25" t="n">
-        <f aca="false">Q38/$D$136</f>
-        <v>12.6099065948955</v>
-      </c>
-      <c r="R202" s="25" t="n">
-        <f aca="false">R38/$D$136</f>
-        <v>13.2599578044205</v>
+      <c r="A202" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F202" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I203" s="22" t="n">
-        <f aca="false">I38/I204</f>
-        <v>8.01942352450795</v>
-      </c>
-      <c r="J203" s="22" t="n">
-        <f aca="false">J38/J204</f>
-        <v>8.70627506431765</v>
-      </c>
-      <c r="K203" s="22" t="n">
-        <f aca="false">K38/K204</f>
-        <v>9.54348776086506</v>
-      </c>
-      <c r="L203" s="22" t="n">
-        <f aca="false">L38/L204</f>
-        <v>10.3941446544693</v>
-      </c>
-      <c r="M203" s="22" t="n">
-        <f aca="false">M38/M204</f>
-        <v>11.3314439973362</v>
-      </c>
-      <c r="N203" s="22" t="n">
-        <f aca="false">N38/N204</f>
-        <v>12.276323983206</v>
-      </c>
-      <c r="O203" s="22" t="n">
-        <f aca="false">O38/O204</f>
-        <v>13.328796683726</v>
-      </c>
-      <c r="P203" s="22" t="n">
-        <f aca="false">P38/P204</f>
-        <v>14.4101079565413</v>
-      </c>
-      <c r="Q203" s="22" t="n">
-        <f aca="false">Q38/Q204</f>
-        <v>15.6213907194519</v>
-      </c>
-      <c r="R203" s="22" t="n">
-        <f aca="false">R38/R204</f>
-        <v>16.8744575064956</v>
+        <v>212</v>
+      </c>
+      <c r="F203" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="I204" s="41" t="n">
-        <f aca="false">$D$136+I77/$D$135</f>
-        <v>14.3733838317253</v>
-      </c>
-      <c r="J204" s="41" t="n">
-        <f aca="false">I204+J77/$D$135</f>
-        <v>14.0587676634506</v>
-      </c>
-      <c r="K204" s="41" t="n">
-        <f aca="false">J204+K77/$D$135</f>
-        <v>13.7441514951759</v>
-      </c>
-      <c r="L204" s="41" t="n">
-        <f aca="false">K204+L77/$D$135</f>
-        <v>13.4295353269012</v>
-      </c>
-      <c r="M204" s="41" t="n">
-        <f aca="false">L204+M77/$D$135</f>
-        <v>13.1149191586265</v>
-      </c>
-      <c r="N204" s="41" t="n">
-        <f aca="false">M204+N77/$D$135</f>
-        <v>12.8003029903518</v>
-      </c>
-      <c r="O204" s="41" t="n">
-        <f aca="false">N204+O77/$D$135</f>
-        <v>12.4856868220771</v>
-      </c>
-      <c r="P204" s="41" t="n">
-        <f aca="false">O204+P77/$D$135</f>
-        <v>12.1710706538024</v>
-      </c>
-      <c r="Q204" s="41" t="n">
-        <f aca="false">P204+Q77/$D$135</f>
-        <v>11.8564544855277</v>
-      </c>
-      <c r="R204" s="41" t="n">
-        <f aca="false">Q204+R77/$D$135</f>
-        <v>11.5418383172529</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="206" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="42" t="s">
-        <v>211</v>
+      <c r="A204" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F204" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F205" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F206" s="21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D207" s="31" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G208" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H208" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I208" s="2" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="3" t="s">
+      <c r="F207" s="21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G207" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D209" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E209" s="32" t="n">
-        <v>22</v>
-      </c>
-      <c r="F209" s="22" t="n">
-        <f aca="false">D209*E209</f>
-        <v>198</v>
-      </c>
-      <c r="G209" s="22" t="n">
-        <f aca="false">F209/(1+$D$207)^K148</f>
-        <v>163.843581645519</v>
-      </c>
-      <c r="H209" s="21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I209" s="41" t="n">
-        <f aca="false">G209*H209</f>
-        <v>32.7687163291038</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D210" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E210" s="32" t="n">
-        <v>28</v>
-      </c>
-      <c r="F210" s="22" t="n">
-        <f aca="false">D210*E210</f>
-        <v>280</v>
-      </c>
-      <c r="G210" s="22" t="n">
-        <f aca="false">F210/(1+$D$207)^K148</f>
-        <v>231.697994246189</v>
-      </c>
-      <c r="H210" s="21" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I210" s="41" t="n">
-        <f aca="false">G210*H210</f>
-        <v>104.264097410785</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D211" s="4" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="E211" s="32" t="n">
-        <v>32</v>
-      </c>
-      <c r="F211" s="22" t="n">
-        <f aca="false">D211*E211</f>
-        <v>342.4</v>
-      </c>
-      <c r="G211" s="22" t="n">
-        <f aca="false">F211/(1+$D$207)^K148</f>
-        <v>283.333547249625</v>
-      </c>
-      <c r="H211" s="21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I211" s="41" t="n">
-        <f aca="false">G211*H211</f>
-        <v>85.0000641748875</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D212" s="4" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E212" s="32" t="n">
-        <v>36</v>
-      </c>
-      <c r="F212" s="22" t="n">
-        <f aca="false">D212*E212</f>
-        <v>428.4</v>
-      </c>
-      <c r="G212" s="22" t="n">
-        <f aca="false">F212/(1+$D$207)^K148</f>
-        <v>354.497931196669</v>
-      </c>
-      <c r="H212" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I212" s="41" t="n">
-        <f aca="false">G212*H212</f>
-        <v>17.7248965598334</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D214" s="25" t="n">
-        <f aca="false">SUM(I209:I212)</f>
-        <v>239.75777447461</v>
-      </c>
-      <c r="E214" s="43" t="n">
-        <f aca="false">SUM(H209:H212)</f>
-        <v>1</v>
-      </c>
-      <c r="F214" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="226" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="42" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="I227" s="4" t="n">
-        <v>478.1</v>
-      </c>
-      <c r="J227" s="4" t="n">
-        <v>520</v>
-      </c>
-      <c r="K227" s="4" t="n">
-        <v>554.9</v>
-      </c>
-    </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="I228" s="43" t="n">
-        <f aca="false">I26/I227-1</f>
-        <v>-0.077325538590253</v>
-      </c>
-      <c r="J228" s="43" t="n">
-        <f aca="false">J26/J227-1</f>
-        <v>-0.102468772538461</v>
-      </c>
-      <c r="K228" s="43" t="n">
-        <f aca="false">K26/K227-1</f>
-        <v>-0.112658800891332</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="I229" s="4" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="J229" s="4" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="K229" s="4" t="n">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="I230" s="43" t="n">
-        <f aca="false">I203/I229-1</f>
-        <v>-0.0845406935493211</v>
-      </c>
-      <c r="J230" s="43" t="n">
-        <f aca="false">J203/J229-1</f>
-        <v>-0.0987292894081108</v>
-      </c>
-      <c r="K230" s="43" t="n">
-        <f aca="false">K203/K229-1</f>
-        <v>-0.108085255993919</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="14" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="235" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G236" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F237" s="21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G237" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F238" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G238" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F239" s="21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F240" s="21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G240" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="F241" s="21" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G241" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F242" s="21" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G242" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="F243" s="21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G243" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="244" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="15" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="B244" s="16"/>
       <c r="C244" s="16"/>
@@ -11320,7 +10879,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="D245" s="31" t="n">
         <v>0.0455</v>
@@ -11328,7 +10887,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="D246" s="31" t="n">
         <v>-0.0023</v>
@@ -11336,7 +10895,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="D247" s="31" t="n">
         <v>0.0432</v>
@@ -11344,7 +10903,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="D248" s="31" t="n">
         <v>0.0446</v>
@@ -11352,7 +10911,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="D249" s="31" t="n">
         <v>0.0878</v>
@@ -11360,7 +10919,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="D250" s="31" t="n">
         <v>0</v>
@@ -11368,7 +10927,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="D251" s="4" t="n">
         <v>1.065</v>
@@ -11376,7 +10935,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="D252" s="31" t="n">
         <v>0</v>
@@ -11384,59 +10943,59 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D253" s="44" t="n">
+        <v>231</v>
+      </c>
+      <c r="D253" s="42" t="n">
         <f aca="false">D247+D251*D248+D252</f>
         <v>0.090699</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="D254" s="31" t="n">
         <v>0.0477</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D255" s="45" t="n">
+        <v>235</v>
+      </c>
+      <c r="D255" s="43" t="n">
         <v>0.0358</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D256" s="44" t="n">
+        <v>236</v>
+      </c>
+      <c r="D256" s="42" t="n">
         <f aca="false">D253*(1-D262)+D255*D262</f>
         <v>0.0894692624</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D257" s="46" t="n">
+        <v>237</v>
+      </c>
+      <c r="D257" s="44" t="n">
         <f aca="false">$D$138-D247</f>
         <v>0</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="D258" s="31" t="n">
         <v>0</v>
@@ -11444,100 +11003,98 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D259" s="44" t="n">
+        <v>240</v>
+      </c>
+      <c r="D259" s="42" t="n">
         <f aca="false">D256+D258</f>
         <v>0.0894692624</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D260" s="46" t="n">
+        <v>241</v>
+      </c>
+      <c r="D260" s="44" t="n">
         <f aca="false">I149-D259</f>
         <v>3.0737599999997E-005</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="D262" s="31" t="n">
         <v>0.0224</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D263" s="44" t="n">
+        <v>246</v>
+      </c>
+      <c r="D263" s="42" t="n">
         <f aca="false">1-D262</f>
         <v>0.9776</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="D264" s="46" t="n">
+        <v>247</v>
+      </c>
+      <c r="D264" s="44" t="n">
         <f aca="false">D262+D263</f>
         <v>1</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D265" s="45" t="n">
+        <v>248</v>
+      </c>
+      <c r="D265" s="43" t="n">
         <f aca="false">D253*D263</f>
         <v>0.0886673424</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D266" s="45" t="n">
+        <v>249</v>
+      </c>
+      <c r="D266" s="43" t="n">
         <f aca="false">D255*D262</f>
         <v>0.00080192</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D267" s="44" t="n">
+        <v>250</v>
+      </c>
+      <c r="D267" s="42" t="n">
         <f aca="false">D265+D266</f>
         <v>0.0894692624</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>251</v>
+      </c>
+    </row>
     <row r="271" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="272" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="273" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="274" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="275" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="15" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="B275" s="16"/>
       <c r="C275" s="16"/>
@@ -11558,7 +11115,6 @@
       <c r="R275" s="16"/>
       <c r="S275" s="16"/>
     </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
         <v>10</v>
@@ -11626,7 +11182,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="D278" s="20" t="n">
         <f aca="false">D28/D26</f>
@@ -11689,7 +11245,6 @@
         <v>0.484</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
         <v>112</v>
@@ -11873,10 +11428,6 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C2"/>
@@ -11901,48 +11452,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P130"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>255</v>
+      </c>
+    </row>
     <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -11954,164 +11504,161 @@
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="48" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="46" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$138+-0.005</f>
         <v>0.0382</v>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="46" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$138+-0.0025</f>
         <v>0.0407</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="46" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$138+0</f>
         <v>0.0432</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="46" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$138+0.0025</f>
         <v>0.0457</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="46" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$138+0.005</f>
         <v>0.0482</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.02</f>
         <v>0.0666</v>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A8)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+B$7)/($A8-B$7)*(1+$A8)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>351.153983730015</v>
-      </c>
-      <c r="C8" s="49" t="n">
+        <v>351.153983730014</v>
+      </c>
+      <c r="C8" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A8)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+C$7)/($A8-C$7)*(1+$A8)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>378.610784883619</v>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A8)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+D$7)/($A8-D$7)*(1+$A8)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>411.934423890558</v>
-      </c>
-      <c r="E8" s="49" t="n">
+        <v>411.934423890557</v>
+      </c>
+      <c r="E8" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A8)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+E$7)/($A8-E$7)*(1+$A8)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>453.230225339347</v>
       </c>
-      <c r="F8" s="49" t="n">
+      <c r="F8" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A8)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+F$7)/($A8-F$7)*(1+$A8)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>505.747711964439</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.01</f>
         <v>0.0766</v>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A9)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+B$7)/($A9-B$7)*(1+$A9)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>258.893915555448</v>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A9)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+C$7)/($A9-C$7)*(1+$A9)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>272.465187245614</v>
-      </c>
-      <c r="D9" s="49" t="n">
+        <v>272.465187245613</v>
+      </c>
+      <c r="D9" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A9)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+D$7)/($A9-D$7)*(1+$A9)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>288.068086434307</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A9)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+E$7)/($A9-E$7)*(1+$A9)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>306.195726592045</v>
-      </c>
-      <c r="F9" s="49" t="n">
+        <v>306.195726592044</v>
+      </c>
+      <c r="F9" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A9)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+F$7)/($A9-F$7)*(1+$A9)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>327.514852693046</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="n">
+        <v>327.514852693045</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0</f>
         <v>0.0866</v>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A10)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+B$7)/($A10-B$7)*(1+$A10)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>204.815560902181</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A10)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+C$7)/($A10-C$7)*(1+$A10)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>212.622369015756</v>
       </c>
-      <c r="D10" s="50" t="n">
+      <c r="D10" s="48" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A10)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+D$7)/($A10-D$7)*(1+$A10)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>221.328578985733</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A10)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+E$7)/($A10-E$7)*(1+$A10)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>231.099117802897</v>
-      </c>
-      <c r="F10" s="49" t="n">
+        <v>231.099117802896</v>
+      </c>
+      <c r="F10" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A10)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+F$7)/($A10-F$7)*(1+$A10)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>242.141862195211</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.01</f>
         <v>0.0966</v>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A11)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+B$7)/($A11-B$7)*(1+$A11)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>169.301688184186</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A11)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+C$7)/($A11-C$7)*(1+$A11)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>174.229949889999</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A11)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+D$7)/($A11-D$7)*(1+$A11)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>179.619659321076</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A11)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+E$7)/($A11-E$7)*(1+$A11)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>185.53880975717</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A11)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+F$7)/($A11-F$7)*(1+$A11)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>192.069442676332</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="n">
+        <v>192.069442676331</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.02</f>
         <v>0.1066</v>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A12)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+B$7)/($A12-B$7)*(1+$A12)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>144.207366538105</v>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A12)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+C$7)/($A12-C$7)*(1+$A12)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>147.520659381795</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A12)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+D$7)/($A12-D$7)*(1+$A12)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>151.095252922937</v>
       </c>
-      <c r="E12" s="49" t="n">
+      <c r="E12" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A12)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+E$7)/($A12-E$7)*(1+$A12)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>154.96332705038</v>
       </c>
-      <c r="F12" s="49" t="n">
+      <c r="F12" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A12)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+F$7)/($A12-F$7)*(1+$A12)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>159.162571907912</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -12123,164 +11670,161 @@
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="51" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="49" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139+-1</f>
         <v>17</v>
       </c>
-      <c r="C17" s="51" t="n">
+      <c r="C17" s="49" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139+-0.5</f>
         <v>17.5</v>
       </c>
-      <c r="D17" s="51" t="n">
+      <c r="D17" s="49" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139+0</f>
         <v>18</v>
       </c>
-      <c r="E17" s="51" t="n">
+      <c r="E17" s="49" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139+0.5</f>
         <v>18.5</v>
       </c>
-      <c r="F17" s="51" t="n">
+      <c r="F17" s="49" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139+1</f>
         <v>19</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="44" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.02</f>
         <v>0.0666</v>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A18)^-('Financial Model &amp; DCF'!$I$148:$R$148))+B$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A18)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>234.977101061998</v>
-      </c>
-      <c r="C18" s="49" t="n">
+        <v>234.977101061999</v>
+      </c>
+      <c r="C18" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A18)^-('Financial Model &amp; DCF'!$I$148:$R$148))+C$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A18)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>239.703617449083</v>
       </c>
-      <c r="D18" s="49" t="n">
+      <c r="D18" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A18)^-('Financial Model &amp; DCF'!$I$148:$R$148))+D$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A18)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>244.430133836167</v>
       </c>
-      <c r="E18" s="49" t="n">
+      <c r="E18" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A18)^-('Financial Model &amp; DCF'!$I$148:$R$148))+E$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A18)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>249.156650223251</v>
       </c>
-      <c r="F18" s="49" t="n">
+      <c r="F18" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A18)^-('Financial Model &amp; DCF'!$I$148:$R$148))+F$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A18)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>253.883166610335</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="44" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.01</f>
         <v>0.0766</v>
       </c>
-      <c r="B19" s="49" t="n">
+      <c r="B19" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A19)^-('Financial Model &amp; DCF'!$I$148:$R$148))+B$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A19)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>218.445715741315</v>
       </c>
-      <c r="C19" s="49" t="n">
+      <c r="C19" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A19)^-('Financial Model &amp; DCF'!$I$148:$R$148))+C$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A19)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>222.783486003335</v>
       </c>
-      <c r="D19" s="49" t="n">
+      <c r="D19" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A19)^-('Financial Model &amp; DCF'!$I$148:$R$148))+D$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A19)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>227.121256265354</v>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A19)^-('Financial Model &amp; DCF'!$I$148:$R$148))+E$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A19)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>231.459026527373</v>
-      </c>
-      <c r="F19" s="49" t="n">
+        <v>231.459026527374</v>
+      </c>
+      <c r="F19" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A19)^-('Financial Model &amp; DCF'!$I$148:$R$148))+F$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A19)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>235.796796789393</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="44" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0</f>
         <v>0.0866</v>
       </c>
-      <c r="B20" s="49" t="n">
+      <c r="B20" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A20)^-('Financial Model &amp; DCF'!$I$148:$R$148))+B$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A20)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>203.328362663313</v>
       </c>
-      <c r="C20" s="49" t="n">
+      <c r="C20" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A20)^-('Financial Model &amp; DCF'!$I$148:$R$148))+C$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A20)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>207.312520691132</v>
       </c>
-      <c r="D20" s="50" t="n">
+      <c r="D20" s="48" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A20)^-('Financial Model &amp; DCF'!$I$148:$R$148))+D$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A20)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>211.296678718951</v>
       </c>
-      <c r="E20" s="49" t="n">
+      <c r="E20" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A20)^-('Financial Model &amp; DCF'!$I$148:$R$148))+E$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A20)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>215.28083674677</v>
       </c>
-      <c r="F20" s="49" t="n">
+      <c r="F20" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A20)^-('Financial Model &amp; DCF'!$I$148:$R$148))+F$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A20)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>219.264994774589</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="44" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.01</f>
         <v>0.0966</v>
       </c>
-      <c r="B21" s="49" t="n">
+      <c r="B21" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A21)^-('Financial Model &amp; DCF'!$I$148:$R$148))+B$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A21)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>189.489906841537</v>
       </c>
-      <c r="C21" s="49" t="n">
+      <c r="C21" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A21)^-('Financial Model &amp; DCF'!$I$148:$R$148))+C$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A21)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>193.152130637928</v>
       </c>
-      <c r="D21" s="49" t="n">
+      <c r="D21" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A21)^-('Financial Model &amp; DCF'!$I$148:$R$148))+D$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A21)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>196.81435443432</v>
       </c>
-      <c r="E21" s="49" t="n">
+      <c r="E21" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A21)^-('Financial Model &amp; DCF'!$I$148:$R$148))+E$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A21)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>200.476578230711</v>
       </c>
-      <c r="F21" s="49" t="n">
+      <c r="F21" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A21)^-('Financial Model &amp; DCF'!$I$148:$R$148))+F$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A21)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>204.138802027103</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="44" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.02</f>
         <v>0.1066</v>
       </c>
-      <c r="B22" s="49" t="n">
+      <c r="B22" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A22)^-('Financial Model &amp; DCF'!$I$148:$R$148))+B$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A22)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>176.809313565419</v>
       </c>
-      <c r="C22" s="49" t="n">
+      <c r="C22" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A22)^-('Financial Model &amp; DCF'!$I$148:$R$148))+C$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A22)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>180.178192292937</v>
       </c>
-      <c r="D22" s="49" t="n">
+      <c r="D22" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A22)^-('Financial Model &amp; DCF'!$I$148:$R$148))+D$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A22)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>183.547071020456</v>
       </c>
-      <c r="E22" s="49" t="n">
+      <c r="E22" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A22)^-('Financial Model &amp; DCF'!$I$148:$R$148))+E$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A22)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>186.915949747974</v>
       </c>
-      <c r="F22" s="49" t="n">
+      <c r="F22" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A22)^-('Financial Model &amp; DCF'!$I$148:$R$148))+F$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A22)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>190.284828475492</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -12292,163 +11836,161 @@
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="52" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="50" t="n">
         <v>0.7</v>
       </c>
-      <c r="C28" s="52" t="n">
+      <c r="C28" s="50" t="n">
         <v>0.85</v>
       </c>
-      <c r="D28" s="52" t="n">
+      <c r="D28" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="52" t="n">
+      <c r="E28" s="50" t="n">
         <v>1.15</v>
       </c>
-      <c r="F28" s="52" t="n">
+      <c r="F28" s="50" t="n">
         <v>1.3</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="44" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.02</f>
         <v>0.0666</v>
       </c>
-      <c r="B29" s="49" t="n">
+      <c r="B29" s="47" t="n">
         <f aca="false">(B$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A29)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A29-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A29)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>230.136970204354</v>
-      </c>
-      <c r="C29" s="49" t="n">
+        <v>230.136970204353</v>
+      </c>
+      <c r="C29" s="47" t="n">
         <f aca="false">(C$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A29)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A29-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A29)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>279.159624533858</v>
       </c>
-      <c r="D29" s="49" t="n">
+      <c r="D29" s="47" t="n">
         <f aca="false">(D$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A29)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A29-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A29)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>328.182278863362</v>
       </c>
-      <c r="E29" s="49" t="n">
+      <c r="E29" s="47" t="n">
         <f aca="false">(E$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A29)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A29-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A29)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>377.204933192867</v>
-      </c>
-      <c r="F29" s="49" t="n">
+        <v>377.204933192866</v>
+      </c>
+      <c r="F29" s="47" t="n">
         <f aca="false">(F$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A29)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A29-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A29)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>426.227587522371</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="44" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.01</f>
         <v>0.0766</v>
       </c>
-      <c r="B30" s="49" t="n">
+      <c r="B30" s="47" t="n">
         <f aca="false">(B$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A30)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A30-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A30)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>180.725644944881</v>
       </c>
-      <c r="C30" s="49" t="n">
+      <c r="C30" s="47" t="n">
         <f aca="false">(C$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A30)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A30-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A30)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>219.160158147356</v>
       </c>
-      <c r="D30" s="49" t="n">
+      <c r="D30" s="47" t="n">
         <f aca="false">(D$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A30)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A30-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A30)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>257.594671349831</v>
-      </c>
-      <c r="E30" s="49" t="n">
+        <v>257.59467134983</v>
+      </c>
+      <c r="E30" s="47" t="n">
         <f aca="false">(E$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A30)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A30-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A30)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>296.029184552305</v>
       </c>
-      <c r="F30" s="49" t="n">
+      <c r="F30" s="47" t="n">
         <f aca="false">(F$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A30)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A30-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A30)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>334.46369775478</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="44" t="n">
+        <v>334.463697754779</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0</f>
         <v>0.0866</v>
       </c>
-      <c r="B31" s="49" t="n">
+      <c r="B31" s="47" t="n">
         <f aca="false">(B$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A31)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A31-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A31)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>151.82821519664</v>
-      </c>
-      <c r="C31" s="49" t="n">
+        <v>151.828215196639</v>
+      </c>
+      <c r="C31" s="47" t="n">
         <f aca="false">(C$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A31)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A31-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A31)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>184.070422024491</v>
       </c>
-      <c r="D31" s="50" t="n">
+      <c r="D31" s="48" t="n">
         <f aca="false">(D$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A31)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A31-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A31)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>216.312628852342</v>
       </c>
-      <c r="E31" s="49" t="n">
+      <c r="E31" s="47" t="n">
         <f aca="false">(E$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A31)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A31-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A31)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>248.554835680194</v>
-      </c>
-      <c r="F31" s="49" t="n">
+        <v>248.554835680193</v>
+      </c>
+      <c r="F31" s="47" t="n">
         <f aca="false">(F$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A31)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A31-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A31)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>280.797042508045</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="44" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.01</f>
         <v>0.0966</v>
       </c>
-      <c r="B32" s="49" t="n">
+      <c r="B32" s="47" t="n">
         <f aca="false">(B$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A32)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A32-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A32)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>132.161279814389</v>
-      </c>
-      <c r="C32" s="49" t="n">
+        <v>132.161279814388</v>
+      </c>
+      <c r="C32" s="47" t="n">
         <f aca="false">(C$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A32)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A32-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A32)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>160.189143346043</v>
       </c>
-      <c r="D32" s="49" t="n">
+      <c r="D32" s="47" t="n">
         <f aca="false">(D$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A32)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A32-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A32)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>188.217006877698</v>
       </c>
-      <c r="E32" s="49" t="n">
+      <c r="E32" s="47" t="n">
         <f aca="false">(E$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A32)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A32-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A32)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>216.244870409353</v>
       </c>
-      <c r="F32" s="49" t="n">
+      <c r="F32" s="47" t="n">
         <f aca="false">(F$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A32)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A32-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A32)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>244.272733941007</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="44" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.02</f>
         <v>0.1066</v>
       </c>
-      <c r="B33" s="49" t="n">
+      <c r="B33" s="47" t="n">
         <f aca="false">(B$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A33)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A33-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A33)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>117.534188380187</v>
       </c>
-      <c r="C33" s="49" t="n">
+      <c r="C33" s="47" t="n">
         <f aca="false">(C$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A33)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A33-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A33)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>142.427675175942</v>
       </c>
-      <c r="D33" s="49" t="n">
+      <c r="D33" s="47" t="n">
         <f aca="false">(D$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A33)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A33-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A33)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>167.321161971696</v>
       </c>
-      <c r="E33" s="49" t="n">
+      <c r="E33" s="47" t="n">
         <f aca="false">(E$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A33)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A33-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A33)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>192.214648767451</v>
       </c>
-      <c r="F33" s="49" t="n">
+      <c r="F33" s="47" t="n">
         <f aca="false">(F$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A33)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A33-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A33)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>217.108135563205</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -12460,113 +12002,112 @@
       <c r="I35" s="16"/>
       <c r="J35" s="16"/>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="53" t="s">
-        <v>294</v>
-      </c>
-      <c r="C38" s="54" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="C38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!I$145)</f>
         <v>2026</v>
       </c>
-      <c r="D38" s="54" t="n">
+      <c r="D38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!J$145)</f>
         <v>2027</v>
       </c>
-      <c r="E38" s="54" t="n">
+      <c r="E38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!K$145)</f>
         <v>2028</v>
       </c>
-      <c r="F38" s="54" t="n">
+      <c r="F38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!L$145)</f>
         <v>2029</v>
       </c>
-      <c r="G38" s="54" t="n">
+      <c r="G38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!M$145)</f>
         <v>2030</v>
       </c>
-      <c r="H38" s="54" t="n">
+      <c r="H38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!N$145)</f>
         <v>2031</v>
       </c>
-      <c r="I38" s="54" t="n">
+      <c r="I38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!O$145)</f>
         <v>2032</v>
       </c>
-      <c r="J38" s="54" t="n">
+      <c r="J38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!P$145)</f>
         <v>2033</v>
       </c>
-      <c r="K38" s="54" t="n">
+      <c r="K38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!Q$145)</f>
         <v>2034</v>
       </c>
-      <c r="L38" s="54" t="n">
+      <c r="L38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!R$145)</f>
         <v>2035</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B39" s="41" t="n">
+        <v>266</v>
+      </c>
+      <c r="B39" s="53" t="n">
         <f aca="false">SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$N39)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+$O39)/($N39-$O39)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$N39)^-'Financial Model &amp; DCF'!$R$148</f>
         <v>2386.98558943007</v>
       </c>
-      <c r="C39" s="41" t="n">
+      <c r="C39" s="53" t="n">
         <f aca="false">B39*(1+$N39)^'Financial Model &amp; DCF'!I$147-'Financial Model &amp; DCF'!I$158</f>
         <v>2409.38741344359</v>
       </c>
-      <c r="D39" s="41" t="n">
+      <c r="D39" s="53" t="n">
         <f aca="false">C39*(1+$N39)^'Financial Model &amp; DCF'!J$147-'Financial Model &amp; DCF'!J$158</f>
         <v>2536.26376709058</v>
       </c>
-      <c r="E39" s="41" t="n">
+      <c r="E39" s="53" t="n">
         <f aca="false">D39*(1+$N39)^'Financial Model &amp; DCF'!K$147-'Financial Model &amp; DCF'!K$158</f>
-        <v>2669.34462282963</v>
-      </c>
-      <c r="F39" s="41" t="n">
+        <v>2669.34462282962</v>
+      </c>
+      <c r="F39" s="53" t="n">
         <f aca="false">E39*(1+$N39)^'Financial Model &amp; DCF'!L$147-'Financial Model &amp; DCF'!L$158</f>
         <v>2808.64097643651</v>
       </c>
-      <c r="G39" s="41" t="n">
+      <c r="G39" s="53" t="n">
         <f aca="false">F39*(1+$N39)^'Financial Model &amp; DCF'!M$147-'Financial Model &amp; DCF'!M$158</f>
         <v>2954.10065197917</v>
       </c>
-      <c r="H39" s="41" t="n">
+      <c r="H39" s="53" t="n">
         <f aca="false">G39*(1+$N39)^'Financial Model &amp; DCF'!N$147-'Financial Model &amp; DCF'!N$158</f>
         <v>3106.15529585105</v>
       </c>
-      <c r="I39" s="41" t="n">
+      <c r="I39" s="53" t="n">
         <f aca="false">H39*(1+$N39)^'Financial Model &amp; DCF'!O$147-'Financial Model &amp; DCF'!O$158</f>
         <v>3264.86059727423</v>
       </c>
-      <c r="J39" s="41" t="n">
+      <c r="J39" s="53" t="n">
         <f aca="false">I39*(1+$N39)^'Financial Model &amp; DCF'!P$147-'Financial Model &amp; DCF'!P$158</f>
         <v>3431.40102484177</v>
       </c>
-      <c r="K39" s="41" t="n">
+      <c r="K39" s="53" t="n">
         <f aca="false">J39*(1+$N39)^'Financial Model &amp; DCF'!Q$147-'Financial Model &amp; DCF'!Q$158</f>
-        <v>3605.64420813123</v>
-      </c>
-      <c r="L39" s="41" t="n">
+        <v>3605.64420813122</v>
+      </c>
+      <c r="L39" s="53" t="n">
         <f aca="false">K39*(1+$N39)^'Financial Model &amp; DCF'!R$147-'Financial Model &amp; DCF'!R$158</f>
-        <v>3788.71368751245</v>
+        <v>3788.71368751244</v>
       </c>
       <c r="N39" s="31" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.02</f>
@@ -12580,9 +12121,9 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="B40" s="25" t="n">
         <f aca="false">(B39-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12610,7 +12151,7 @@
       </c>
       <c r="H40" s="25" t="n">
         <f aca="false">(H39-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>212.840297920143</v>
+        <v>212.840297920142</v>
       </c>
       <c r="I40" s="25" t="n">
         <f aca="false">(I39-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12629,51 +12170,51 @@
         <v>259.310776655259</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B41" s="41" t="n">
+        <v>268</v>
+      </c>
+      <c r="B41" s="53" t="n">
         <f aca="false">SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$N41)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+$O41)/($N41-$O41)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$N41)^-'Financial Model &amp; DCF'!$R$148</f>
         <v>3157.1568925832</v>
       </c>
-      <c r="C41" s="41" t="n">
+      <c r="C41" s="53" t="n">
         <f aca="false">B41*(1+$N41)^'Financial Model &amp; DCF'!I$147-'Financial Model &amp; DCF'!I$158</f>
         <v>3183.5350857342</v>
       </c>
-      <c r="D41" s="41" t="n">
+      <c r="D41" s="53" t="n">
         <f aca="false">C41*(1+$N41)^'Financial Model &amp; DCF'!J$147-'Financial Model &amp; DCF'!J$158</f>
-        <v>3329.26487953269</v>
-      </c>
-      <c r="E41" s="41" t="n">
+        <v>3329.26487953268</v>
+      </c>
+      <c r="E41" s="53" t="n">
         <f aca="false">D41*(1+$N41)^'Financial Model &amp; DCF'!K$147-'Financial Model &amp; DCF'!K$158</f>
-        <v>3480.29435626741</v>
-      </c>
-      <c r="F41" s="41" t="n">
+        <v>3480.2943562674</v>
+      </c>
+      <c r="F41" s="53" t="n">
         <f aca="false">E41*(1+$N41)^'Financial Model &amp; DCF'!L$147-'Financial Model &amp; DCF'!L$158</f>
         <v>3636.43206433341</v>
       </c>
-      <c r="G41" s="41" t="n">
+      <c r="G41" s="53" t="n">
         <f aca="false">F41*(1+$N41)^'Financial Model &amp; DCF'!M$147-'Financial Model &amp; DCF'!M$158</f>
         <v>3797.40562855921</v>
       </c>
-      <c r="H41" s="41" t="n">
+      <c r="H41" s="53" t="n">
         <f aca="false">G41*(1+$N41)^'Financial Model &amp; DCF'!N$147-'Financial Model &amp; DCF'!N$158</f>
         <v>3963.40847036334</v>
       </c>
-      <c r="I41" s="41" t="n">
+      <c r="I41" s="53" t="n">
         <f aca="false">H41*(1+$N41)^'Financial Model &amp; DCF'!O$147-'Financial Model &amp; DCF'!O$158</f>
         <v>4134.22879078226</v>
       </c>
-      <c r="J41" s="41" t="n">
+      <c r="J41" s="53" t="n">
         <f aca="false">I41*(1+$N41)^'Financial Model &amp; DCF'!P$147-'Financial Model &amp; DCF'!P$158</f>
         <v>4310.75929196211</v>
       </c>
-      <c r="K41" s="41" t="n">
+      <c r="K41" s="53" t="n">
         <f aca="false">J41*(1+$N41)^'Financial Model &amp; DCF'!Q$147-'Financial Model &amp; DCF'!Q$158</f>
-        <v>4492.52688068736</v>
-      </c>
-      <c r="L41" s="41" t="n">
+        <v>4492.52688068735</v>
+      </c>
+      <c r="L41" s="53" t="n">
         <f aca="false">K41*(1+$N41)^'Financial Model &amp; DCF'!R$147-'Financial Model &amp; DCF'!R$158</f>
         <v>4680.28751534931</v>
       </c>
@@ -12689,9 +12230,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="B42" s="25" t="n">
         <f aca="false">(B41-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12707,7 +12248,7 @@
       </c>
       <c r="E42" s="25" t="n">
         <f aca="false">(E41-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>238.312728504045</v>
+        <v>238.312728504044</v>
       </c>
       <c r="F42" s="25" t="n">
         <f aca="false">(F41-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12727,7 +12268,7 @@
       </c>
       <c r="J42" s="25" t="n">
         <f aca="false">(J41-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>294.853097219643</v>
+        <v>294.853097219642</v>
       </c>
       <c r="K42" s="25" t="n">
         <f aca="false">(K41-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12738,53 +12279,53 @@
         <v>320.011609160492</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B43" s="41" t="n">
+        <v>270</v>
+      </c>
+      <c r="B43" s="53" t="n">
         <f aca="false">SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$N43)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+$O43)/($N43-$O43)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$N43)^-'Financial Model &amp; DCF'!$R$148</f>
         <v>5489.26309955965</v>
       </c>
-      <c r="C43" s="41" t="n">
+      <c r="C43" s="53" t="n">
         <f aca="false">B43*(1+$N43)^'Financial Model &amp; DCF'!I$147-'Financial Model &amp; DCF'!I$158</f>
         <v>5533.75240852241</v>
       </c>
-      <c r="D43" s="41" t="n">
+      <c r="D43" s="53" t="n">
         <f aca="false">C43*(1+$N43)^'Financial Model &amp; DCF'!J$147-'Financial Model &amp; DCF'!J$158</f>
-        <v>5772.33597430391</v>
-      </c>
-      <c r="E43" s="41" t="n">
+        <v>5772.3359743039</v>
+      </c>
+      <c r="E43" s="53" t="n">
         <f aca="false">D43*(1+$N43)^'Financial Model &amp; DCF'!K$147-'Financial Model &amp; DCF'!K$158</f>
-        <v>6019.48868835974</v>
-      </c>
-      <c r="F43" s="41" t="n">
+        <v>6019.48868835973</v>
+      </c>
+      <c r="F43" s="53" t="n">
         <f aca="false">E43*(1+$N43)^'Financial Model &amp; DCF'!L$147-'Financial Model &amp; DCF'!L$158</f>
         <v>6275.13085181774</v>
       </c>
-      <c r="G43" s="41" t="n">
+      <c r="G43" s="53" t="n">
         <f aca="false">F43*(1+$N43)^'Financial Model &amp; DCF'!M$147-'Financial Model &amp; DCF'!M$158</f>
         <v>6539.11311400333</v>
       </c>
-      <c r="H43" s="41" t="n">
+      <c r="H43" s="53" t="n">
         <f aca="false">G43*(1+$N43)^'Financial Model &amp; DCF'!N$147-'Financial Model &amp; DCF'!N$158</f>
-        <v>6811.76556176686</v>
-      </c>
-      <c r="I43" s="41" t="n">
+        <v>6811.76556176685</v>
+      </c>
+      <c r="I43" s="53" t="n">
         <f aca="false">H43*(1+$N43)^'Financial Model &amp; DCF'!O$147-'Financial Model &amp; DCF'!O$158</f>
         <v>7093.01829506598</v>
       </c>
-      <c r="J43" s="41" t="n">
+      <c r="J43" s="53" t="n">
         <f aca="false">I43*(1+$N43)^'Financial Model &amp; DCF'!P$147-'Financial Model &amp; DCF'!P$158</f>
         <v>7383.91960141548</v>
       </c>
-      <c r="K43" s="41" t="n">
+      <c r="K43" s="53" t="n">
         <f aca="false">J43*(1+$N43)^'Financial Model &amp; DCF'!Q$147-'Financial Model &amp; DCF'!Q$158</f>
-        <v>7684.14448091108</v>
-      </c>
-      <c r="L43" s="41" t="n">
+        <v>7684.14448091107</v>
+      </c>
+      <c r="L43" s="53" t="n">
         <f aca="false">K43*(1+$N43)^'Financial Model &amp; DCF'!R$147-'Financial Model &amp; DCF'!R$158</f>
-        <v>7994.61631013419</v>
+        <v>7994.61631013418</v>
       </c>
       <c r="N43" s="31" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.02</f>
@@ -12798,9 +12339,9 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="B44" s="25" t="n">
         <f aca="false">(B43-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12808,7 +12349,7 @@
       </c>
       <c r="C44" s="25" t="n">
         <f aca="false">(C43-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>378.117879120535</v>
+        <v>378.117879120534</v>
       </c>
       <c r="D44" s="25" t="n">
         <f aca="false">(D43-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12824,7 +12365,7 @@
       </c>
       <c r="G44" s="25" t="n">
         <f aca="false">(G43-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>446.565639569944</v>
+        <v>446.565639569943</v>
       </c>
       <c r="H44" s="25" t="n">
         <f aca="false">(H43-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12844,101 +12385,79 @@
       </c>
       <c r="L44" s="25" t="n">
         <f aca="false">(L43-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>545.660356082121</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>545.66035608212</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="B45" s="55" t="n">
+        <v>272</v>
+      </c>
+      <c r="B45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
-      <c r="C45" s="55" t="n">
+      <c r="C45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
-      <c r="D45" s="55" t="n">
+      <c r="D45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
-      <c r="E45" s="55" t="n">
+      <c r="E45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
-      <c r="F45" s="55" t="n">
+      <c r="F45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
-      <c r="G45" s="55" t="n">
+      <c r="G45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
-      <c r="H45" s="55" t="n">
+      <c r="H45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
-      <c r="I45" s="55" t="n">
+      <c r="I45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
-      <c r="J45" s="55" t="n">
+      <c r="J45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
-      <c r="K45" s="55" t="n">
+      <c r="K45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
-      <c r="L45" s="55" t="n">
+      <c r="L45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>333.74</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="B46" s="25" t="n">
         <f aca="false">B40*$P$39+B42*$P$41+B44*$P$43</f>
         <v>242.897849846067</v>
       </c>
-      <c r="P46" s="43" t="n">
+      <c r="P46" s="55" t="n">
         <f aca="false">P39+P41+P43</f>
         <v>1</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>274</v>
+      </c>
+    </row>
     <row r="70" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -12950,68 +12469,66 @@
       <c r="I70" s="16"/>
       <c r="J70" s="16"/>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="B72" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="B73" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="B74" s="22" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$136+B72</f>
         <v>14.688</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="B75" s="22" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$170+B73</f>
         <v>3145.1441237374</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="B76" s="25" t="n">
         <f aca="false">B75/B74</f>
         <v>214.130182716326</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="B77" s="39" t="n">
         <f aca="false">B76/'Financial Model &amp; DCF'!$D$135-1</f>
         <v>-0.358392213350734</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="80" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="15" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
@@ -13023,53 +12540,49 @@
       <c r="I80" s="16"/>
       <c r="J80" s="16"/>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>291</v>
+      </c>
+    </row>
     <row r="93" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="15" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
@@ -13081,39 +12594,24 @@
       <c r="I93" s="16"/>
       <c r="J93" s="16"/>
     </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="56" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>295</v>
+      </c>
+    </row>
     <row r="112" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="15" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="B112" s="16"/>
       <c r="C112" s="16"/>
@@ -13125,40 +12623,40 @@
       <c r="I112" s="16"/>
       <c r="J112" s="16"/>
     </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="B114" s="21" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="B115" s="22" t="n">
         <f aca="false">-'Financial Model &amp; DCF'!$D$135*(1+B114)*'Financial Model &amp; DCF'!$D$136</f>
         <v>-4901.97312</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="B116" s="32" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139</f>
         <v>18</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>329</v>
+        <v>301</v>
       </c>
       <c r="B117" s="22" t="n">
         <f aca="false">B115</f>
@@ -13205,58 +12703,57 @@
         <v>5175.89250070878</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="B118" s="40" t="n">
         <f aca="false">IFERROR(IRR(B117:L117),"n/m - owner cash flows never turn positive")</f>
         <v>0.0245027801065895</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="B119" s="57" t="n">
         <f aca="false">SUM(C117:L117)/-B115</f>
         <v>1.24865892791937</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="51" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="49" t="n">
         <f aca="false">$B$116+-2</f>
         <v>16</v>
       </c>
-      <c r="C123" s="51" t="n">
+      <c r="C123" s="49" t="n">
         <f aca="false">$B$116+-1</f>
         <v>17</v>
       </c>
-      <c r="D123" s="51" t="n">
+      <c r="D123" s="49" t="n">
         <f aca="false">$B$116+0</f>
         <v>18</v>
       </c>
-      <c r="E123" s="51" t="n">
+      <c r="E123" s="49" t="n">
         <f aca="false">$B$116+1</f>
         <v>19</v>
       </c>
-      <c r="F123" s="51" t="n">
+      <c r="F123" s="49" t="n">
         <f aca="false">$B$116+2</f>
         <v>20</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="40" t="n">
         <v>-0.2</v>
       </c>
@@ -13281,7 +12778,7 @@
         <v>0.0538084987692453</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="40" t="n">
         <v>-0.1</v>
       </c>
@@ -13306,7 +12803,7 @@
         <v>0.0414692328309485</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="40" t="n">
         <v>0</v>
       </c>
@@ -13331,7 +12828,7 @@
         <v>0.0305538627154753</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="40" t="n">
         <v>0.1</v>
       </c>
@@ -13356,7 +12853,7 @@
         <v>0.0207782948777291</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="40" t="n">
         <v>0.2</v>
       </c>
@@ -13381,10 +12878,9 @@
         <v>0.0119348920012461</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>334</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
